--- a/日语/N2/练习/答案.xlsx
+++ b/日语/N2/练习/答案.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10149\Desktop\n2测试题\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\doc\study\日语\N2\练习\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D59CB1-F4DC-4AE8-864D-E284F2AAF1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD207E1-19DE-4647-AED5-45C6917B5E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,13 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="6">
   <si>
     <t>题号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>狗答案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -56,11 +52,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MD</t>
+    <t>我的答案</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我自己钱买的</t>
+    <t>正确与否</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -145,31 +141,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -453,36 +429,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>55</v>
       </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5">
-        <v>2</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>56</v>
       </c>
@@ -493,10 +471,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>57</v>
       </c>
@@ -507,10 +485,10 @@
         <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>58</v>
       </c>
@@ -521,10 +499,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>59</v>
       </c>
@@ -535,10 +513,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>60</v>
       </c>
@@ -549,229 +527,223 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>61</v>
       </c>
-      <c r="B8" s="5">
-        <v>2</v>
-      </c>
-      <c r="C8" s="5">
-        <v>4</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>62</v>
       </c>
-      <c r="B9" s="5">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>63</v>
       </c>
-      <c r="B10" s="5">
-        <v>3</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>64</v>
       </c>
-      <c r="B11" s="5">
-        <v>4</v>
-      </c>
-      <c r="C11" s="5">
-        <v>4</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="B11" s="1">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>65</v>
       </c>
-      <c r="B12" s="5">
-        <v>2</v>
-      </c>
-      <c r="C12" s="5">
-        <v>4</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>66</v>
       </c>
-      <c r="B13" s="5">
-        <v>4</v>
-      </c>
-      <c r="C13" s="5">
-        <v>4</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="B13" s="1">
+        <v>4</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>67</v>
       </c>
-      <c r="B14" s="5">
-        <v>2</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>68</v>
       </c>
-      <c r="B15" s="5">
-        <v>3</v>
-      </c>
-      <c r="C15" s="5">
-        <v>3</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="B15" s="1">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>69</v>
       </c>
-      <c r="B16" s="5">
-        <v>4</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>3</v>
+      <c r="B16" s="1">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>70</v>
       </c>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>2</v>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>71</v>
       </c>
-      <c r="B18" s="5">
-        <v>3</v>
-      </c>
-      <c r="C18" s="5">
-        <v>3</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>2</v>
+      <c r="B18" s="1">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>72</v>
       </c>
-      <c r="B19" s="5">
-        <v>2</v>
-      </c>
-      <c r="C19" s="5">
-        <v>4</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>3</v>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>73</v>
       </c>
-      <c r="B20" s="5">
-        <v>4</v>
-      </c>
-      <c r="C20" s="5">
-        <v>4</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>2</v>
+      <c r="B20" s="1">
+        <v>4</v>
+      </c>
+      <c r="C20" s="1">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>74</v>
       </c>
-      <c r="B21" s="5">
-        <v>2</v>
-      </c>
-      <c r="C21" s="5">
-        <v>2</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>2</v>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>75</v>
       </c>
-      <c r="B22" s="5">
-        <v>3</v>
-      </c>
-      <c r="C22" s="5">
-        <v>3</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>2</v>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:D22">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B2&lt;&gt;$C2</formula>
     </cfRule>
   </conditionalFormatting>
